--- a/output_data/charts/0500000US39101.xlsx
+++ b/output_data/charts/0500000US39101.xlsx
@@ -161,10 +161,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2012</c:v>
                 </c:pt>
@@ -200,51 +200,57 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.266317808525298</c:v>
+                  <c:v>1.210450846384477</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.364670204700531</c:v>
+                  <c:v>1.376689657722961</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.490127902644977</c:v>
+                  <c:v>1.538911851838711</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.43490514160022</c:v>
+                  <c:v>1.40740995325818</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.588715295054234</c:v>
+                  <c:v>1.582164062759147</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.585518474374255</c:v>
+                  <c:v>1.599648704598206</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.693936176856304</c:v>
+                  <c:v>1.717354649347405</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.75576948829735</c:v>
+                  <c:v>1.763209189518949</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.869884786329704</c:v>
+                  <c:v>1.873641609832871</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.086610337003578</c:v>
+                  <c:v>2.074082322972202</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.032278923683967</c:v>
+                  <c:v>2.01248399910263</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2.060989791962786</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.170295883672141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -652,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -671,7 +677,7 @@
         <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>1.266317808525298</v>
+        <v>1.210450846384477</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -679,7 +685,7 @@
         <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>1.364670204700531</v>
+        <v>1.376689657722961</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -687,7 +693,7 @@
         <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>1.490127902644977</v>
+        <v>1.538911851838711</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -695,7 +701,7 @@
         <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>1.43490514160022</v>
+        <v>1.40740995325818</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -703,7 +709,7 @@
         <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>1.588715295054234</v>
+        <v>1.582164062759147</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -711,7 +717,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>1.585518474374255</v>
+        <v>1.599648704598206</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -719,7 +725,7 @@
         <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>1.693936176856304</v>
+        <v>1.717354649347405</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -727,7 +733,7 @@
         <v>2019</v>
       </c>
       <c r="B9" s="1">
-        <v>1.75576948829735</v>
+        <v>1.763209189518949</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -735,7 +741,7 @@
         <v>2020</v>
       </c>
       <c r="B10" s="1">
-        <v>1.869884786329704</v>
+        <v>1.873641609832871</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -743,7 +749,7 @@
         <v>2021</v>
       </c>
       <c r="B11" s="1">
-        <v>2.086610337003578</v>
+        <v>2.074082322972202</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -751,7 +757,7 @@
         <v>2022</v>
       </c>
       <c r="B12" s="1">
-        <v>2.032278923683967</v>
+        <v>2.01248399910263</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -760,6 +766,14 @@
       </c>
       <c r="B13" s="1">
         <v>2.060989791962786</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2.170295883672141</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39101.xlsx
+++ b/output_data/charts/0500000US39101.xlsx
@@ -161,47 +161,32 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2012</c:v>
+                  <c:v>2017</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2013</c:v>
+                  <c:v>2018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2014</c:v>
+                  <c:v>2019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2015</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2016</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2017</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2018</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -209,47 +194,32 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$14</c:f>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1.210450846384477</c:v>
+                  <c:v>1.599648704598206</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.376689657722961</c:v>
+                  <c:v>1.717354649347405</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.538911851838711</c:v>
+                  <c:v>1.766929040129748</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.40740995325818</c:v>
+                  <c:v>1.873641609832871</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.582164062759147</c:v>
+                  <c:v>2.086610337003577</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.599648704598206</c:v>
+                  <c:v>2.00918484500574</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.717354649347405</c:v>
+                  <c:v>2.051298617392428</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.763209189518949</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.873641609832871</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.074082322972202</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.01248399910263</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.060989791962786</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2.170295883672141</c:v>
                 </c:pt>
               </c:numCache>
@@ -658,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -674,105 +644,65 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="B2" s="1">
-        <v>1.210450846384477</v>
+        <v>1.599648704598206</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="1">
-        <v>1.376689657722961</v>
+        <v>1.717354649347405</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B4" s="1">
-        <v>1.538911851838711</v>
+        <v>1.766929040129748</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="1">
-        <v>1.40740995325818</v>
+        <v>1.873641609832871</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="1">
-        <v>1.582164062759147</v>
+        <v>2.086610337003577</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="B7" s="1">
-        <v>1.599648704598206</v>
+        <v>2.00918484500574</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B8" s="1">
-        <v>1.717354649347405</v>
+        <v>2.051298617392428</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="1">
-        <v>1.763209189518949</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1.873641609832871</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2.074082322972202</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2.01248399910263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2.060989791962786</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="1">
         <v>2.170295883672141</v>
       </c>
     </row>

--- a/output_data/charts/0500000US39101.xlsx
+++ b/output_data/charts/0500000US39101.xlsx
@@ -161,32 +161,47 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -194,32 +209,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>1.210450846384477</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2481739677139</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.490127902644977</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.399676931536981</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.582164062759147</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1.599648704598206</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>1.717354649347405</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>1.766929040129748</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
                   <c:v>1.873641609832871</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="9">
                   <c:v>2.086610337003577</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>2.00918484500574</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
                   <c:v>2.051298617392428</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
                   <c:v>2.170295883672141</c:v>
                 </c:pt>
               </c:numCache>
@@ -628,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -644,65 +674,105 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>1.599648704598206</v>
+        <v>1.210450846384477</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>1.717354649347405</v>
+        <v>1.2481739677139</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>1.766929040129748</v>
+        <v>1.490127902644977</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>1.873641609832871</v>
+        <v>1.399676931536981</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>2.086610337003577</v>
+        <v>1.582164062759147</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>2.00918484500574</v>
+        <v>1.599648704598206</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>2.051298617392428</v>
+        <v>1.717354649347405</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.766929040129748</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1.873641609832871</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2.086610337003577</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2.00918484500574</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2.051298617392428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
         <v>2024</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B14" s="1">
         <v>2.170295883672141</v>
       </c>
     </row>
